--- a/output/pdf_financials_xlsx/GLDC.xlsx
+++ b/output/pdf_financials_xlsx/GLDC.xlsx
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.768435</v>
+        <v>-0.768435</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-5.766621</v>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.768435</v>
+        <v>-0.768435</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-5.766621</v>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.768435</v>
+        <v>-0.768435</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-5.766621</v>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-15.3687</v>
+        <v>15.3687</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>3.581752</v>
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.768435</v>
+        <v>-0.768435</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-5.770893</v>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.768435</v>
+        <v>-0.768435</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-5.770893</v>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1620.247960022772</v>
+        <v>-1620.247960022772</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-1230.268229455355</v>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1620.247960022772</v>
+        <v>-1620.247960022772</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>-1229.357502835362</v>
@@ -67787,7 +67787,7 @@
         </is>
       </c>
       <c r="F625" s="5" t="n">
-        <v>0.768435</v>
+        <v>-0.768435</v>
       </c>
       <c r="G625" t="inlineStr">
         <is>
@@ -68181,7 +68181,7 @@
         </is>
       </c>
       <c r="F629" s="5" t="n">
-        <v>0.768435</v>
+        <v>-0.768435</v>
       </c>
       <c r="G629" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/GLDC.xlsx
+++ b/output/pdf_financials_xlsx/GLDC.xlsx
@@ -1041,13 +1041,13 @@
         <v>0.515862</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>6.331093</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>1.215827</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>0.796472</v>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.007516</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0.004272</v>
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.768435</v>
+        <v>-0.7759509999999999</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-5.770893</v>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.768435</v>
+        <v>-0.7759509999999999</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-5.770893</v>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-1620.247960022772</v>
+        <v>-1636.095473042781</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-1230.268229455355</v>
@@ -2849,40 +2849,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.39166</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.132007</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.032661</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.0027</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.808935</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.003157</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.710271</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.024387</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.323923</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.13413</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.962338</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>3.473561</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>8.589522000000001</v>
@@ -2959,40 +2959,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.39166</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.132007</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.032661</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.0027</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.808935</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.003157</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.710271</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.024387</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.323923</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.13413</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.962338</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>3.473561</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>8.589522000000001</v>
@@ -3619,40 +3619,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.39166</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.767446</v>
+        <v>0.635439</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.041059</v>
+        <v>0.008397999999999999</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.062453</v>
+        <v>0.059753</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.929029</v>
+        <v>0.120094</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.001165</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.749605</v>
+        <v>0.039334</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.133372</v>
+        <v>0.108985</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.365616</v>
+        <v>0.041693</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.17323</v>
+        <v>0.0391</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.072886</v>
+        <v>0.110548</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>3.547791</v>
+        <v>0.07423</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.19342</v>
@@ -7863,16 +7863,16 @@
         <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.032292</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.096877</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.101059</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.066056</v>
       </c>
     </row>
     <row r="125">
@@ -7918,16 +7918,16 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.032292</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.096877</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.101059</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.066056</v>
       </c>
     </row>
     <row r="126">
@@ -20178,7 +20178,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -40458,7 +40458,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E339" s="5" t="n">
@@ -42812,7 +42812,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E363" s="5" t="n">
@@ -45602,7 +45602,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
@@ -47668,7 +47672,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
           <t>-</t>
@@ -64698,7 +64706,7 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
@@ -66804,7 +66812,7 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
@@ -67194,7 +67202,7 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">

--- a/output/pdf_financials_xlsx/GLDC.xlsx
+++ b/output/pdf_financials_xlsx/GLDC.xlsx
@@ -6578,16 +6578,16 @@
         <v>0.001611</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>-0.020511</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>0.015804</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>-0.075761</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>-0.040074</v>
       </c>
       <c r="N101" s="3" t="n">
         <v>-0.263264</v>
@@ -6853,16 +6853,16 @@
         <v>-0.126302</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.00859</v>
+        <v>-0.011921</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-0.107036</v>
+        <v>-0.09123199999999999</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.493486</v>
+        <v>0.417725</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>-0.08903899999999999</v>
+        <v>-0.129113</v>
       </c>
       <c r="N106" s="3" t="n">
         <v>1.451271</v>
@@ -7055,16 +7055,16 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.002327</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.001465</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.000459</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>-0.027589</v>
       </c>
       <c r="H110" s="3" t="n">
         <v>0</v>
@@ -7082,19 +7082,19 @@
         <v>0</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.028532</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.026549</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.068449</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.113324</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.09546</v>
       </c>
     </row>
     <row r="111">
@@ -44650,7 +44650,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr">
         <is>
           <t>-</t>
@@ -47032,7 +47036,11 @@
           <t>Accretion 10</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E407" t="inlineStr">
         <is>
           <t>-</t>
@@ -49002,7 +49010,11 @@
           <t>Accretion (Note 8)</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -49092,7 +49104,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
           <t>-</t>
@@ -50662,7 +50678,11 @@
           <t>Accretion (Note 5)</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
           <t>-</t>
@@ -54718,7 +54738,11 @@
           <t>Accretion (Note 7)</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E489" t="inlineStr">
         <is>
           <t>-</t>
@@ -58522,7 +58546,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D529" t="inlineStr"/>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E529" t="inlineStr">
         <is>
           <t>-</t>
@@ -60338,7 +60366,11 @@
           <t>Accretion (Note 9) 2,327</t>
         </is>
       </c>
-      <c r="D548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E548" t="inlineStr">
         <is>
           <t>-</t>
